--- a/internal_doc/05.测试设计/story/rename/rename（修改cl基本功能）.xlsx
+++ b/internal_doc/05.测试设计/story/rename/rename（修改cl基本功能）.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="106">
   <si>
     <t>name</t>
   </si>
@@ -476,6 +476,116 @@
   <si>
     <t>1、修改cl操作成功
 2、查看对应cl名修改正确（如查看cs快照中cl名为新名：db.snapshot( SDB_SNAP_COLLECTIONSPACES,{"Name": "csName"} )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志归档过程中修改cl名，重放归档日志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、归档日志成功
+2、重放日志成功，重放完成后查询新cl上数据正确，和cl上插入数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、节点开启日志归档
+2、向归档cl中插入数据，执行更新、删除操作，触发日志归档
+3、归档过程中修改cl名
+4、向新cl中继续插入数据
+5、在后台持续监控归档目录并重放归档日志文件，同时记录状态，如执行./sdbreplay --hostname sdbserver1 --svcname 11810 --path /data/archivelog --watch true --daemon true --status 1.status
+6、检查日志重放结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全量备份过程中修改cl名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修改cl名失败，返回对应错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量备份过程中修改cl名，恢复数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、执行cl所在组执行全量备份数据操作
+2、过程中修改cl名
+3、检查操作结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、cl插入数据，执行增量备份
+2、增量备份过程中修改cl名
+3、新cl插入数据，执行增量备份（可循环执行增量备份，如设置每1分钟执行增量备份）
+4、启动恢复集群，查看集群数据信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、备份数据操作成功
+2、恢复数据成功，恢复集群上存在新cl，旧cl已不存在，查看恢复集群上新cl数据信息和备份数据一致，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改cl名，执行全量备份和恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、cl插入数据
+2、修改cl名，再次插入数据
+3、指定cl所在组，执行全量备份
+4、启动恢复集群，恢复该cl数据信息，检查操作结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、恢复数据失败，返回对应错误信息
+2、查看恢复集群上为旧cl，查看cl数据为修改cl前插入数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备节点执行全量同步过程中，修改cl名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、备节点构造异常，启动后执行全量同步
+2、数据全量同步过程中，修改cl名
+3、检查修改结果，查看备节点上cl名信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修改cl成功，查看cl元数据信息中cl名为新名
+2、备节点全量同步完成后，已同步新cl名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改cl名未同步到备节点，备节点异常执行全量同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修改cl名，构造备节点异常，未同步新cl名
+2、构造备节点异常执行全量同步
+3、检查备节点上cl名信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、备节点全量同步完成后，同步新cl名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改cl后查询cl统计信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、cl执行analyze进行统计信息分析和收集
+2、修改cl名
+3、检查原cl统计信息情况
+4、再次对新cl名执行analyze收集统计信息
+5、检查统计信息情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修改cl名后，查看原cl统计信息已清空
+2、再次对新cl收集统计信息，查看生成新统计信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -693,8 +803,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I22" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I30" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I30"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1013,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -1365,7 +1475,7 @@
     </row>
     <row r="14" spans="1:9" ht="67.5">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="1" t="s">
@@ -1381,16 +1491,16 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" ht="81">
+    <row r="15" spans="1:9" ht="67.5">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="1" t="s">
@@ -1406,40 +1516,41 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" ht="81">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" ht="54">
-      <c r="A16" s="1" t="s">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9" ht="54">
+      <c r="A17" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3">
-        <v>2</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" ht="67.5">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>9</v>
@@ -1454,16 +1565,16 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>68</v>
+        <v>45</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" ht="54">
+    <row r="18" spans="1:9" ht="67.5">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>9</v>
@@ -1478,16 +1589,16 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" ht="67.5">
+    <row r="19" spans="1:9" ht="54">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>9</v>
@@ -1502,105 +1613,267 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9" ht="67.5">
+      <c r="A20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" ht="54">
-      <c r="A20" s="1" t="s">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" ht="54">
+      <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="3">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9" ht="67.5">
-      <c r="A21" s="1" t="s">
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" ht="67.5">
+      <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3">
-        <v>2</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9" ht="108">
-      <c r="A22" s="1" t="s">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" ht="108">
+      <c r="A23" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="121.5">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:9" ht="121.5">
+      <c r="A24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="148.5">
+      <c r="A25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="40.5">
+      <c r="A26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="67.5">
+      <c r="A27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="54">
+      <c r="A28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="40.5">
+      <c r="A29" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="40.5">
+      <c r="A30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
